--- a/data/fmsForecastOutput/File1/RPT_RPT7633743062479QR_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT7633743062479QR_fmsForecastOutput.xlsx
@@ -1887,7 +1887,7 @@
         <v>566.7184588538407</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>593.9065092407632</v>
+        <v>593.9065092407629</v>
       </c>
       <c r="H8" s="148" t="n">
         <v>474.4341254786115</v>
@@ -1902,7 +1902,7 @@
         <v>565.2809616361691</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>593.6532098588118</v>
+        <v>593.6532098588116</v>
       </c>
       <c r="M8" s="151" t="n">
         <v>52896349.07684423</v>
@@ -1917,7 +1917,7 @@
         <v>77801525.31451577</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>90267512.0945241</v>
+        <v>90267512.09452409</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>586.7382173041783</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>614.8867061468775</v>
+        <v>614.8867061468773</v>
       </c>
       <c r="Y8" s="148" t="n">
         <v>491.9239842598317</v>
@@ -1952,7 +1952,7 @@
         <v>585.4963480025333</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>614.6679547025863</v>
+        <v>614.667954702586</v>
       </c>
       <c r="AD8" s="151" t="n">
         <v>52896349.07684423</v>
@@ -1967,7 +1967,7 @@
         <v>77801525.31451577</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>90267512.0945241</v>
+        <v>90267512.09452409</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>682.1607033597045</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>712.1218941358344</v>
+        <v>712.1218941358341</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>581.7182480849186</v>
@@ -2197,7 +2197,7 @@
         <v>680.3079331278037</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>711.7025128655036</v>
+        <v>711.7025128655034</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>79081771.07342969</v>
@@ -2232,7 +2232,7 @@
         <v>703.5392261393408</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>734.4530021037724</v>
+        <v>734.4530021037721</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>600.5347822545243</v>
@@ -2247,7 +2247,7 @@
         <v>701.8663116359357</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>734.0596552581666</v>
+        <v>734.0596552581663</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>79081771.07342969</v>
@@ -2321,7 +2321,7 @@
         <v>1212.465281228247</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>1263.109346696359</v>
+        <v>1263.10934669636</v>
       </c>
       <c r="E11" s="156" t="n">
         <v>1322.265509850169</v>
@@ -2371,7 +2371,7 @@
         <v>1476.343304116993</v>
       </c>
       <c r="U11" s="156" t="n">
-        <v>1538.009421988317</v>
+        <v>1538.009421988318</v>
       </c>
       <c r="V11" s="156" t="n">
         <v>1610.040189979388</v>
@@ -2386,7 +2386,7 @@
         <v>1469.199197303926</v>
       </c>
       <c r="Z11" s="156" t="n">
-        <v>1533.52954115518</v>
+        <v>1533.529541155181</v>
       </c>
       <c r="AA11" s="156" t="n">
         <v>1608.379044570821</v>
@@ -2467,31 +2467,31 @@
         <v>654.0111407501352</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>692.8347449273577</v>
+        <v>692.8347449273579</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>723.8398581678548</v>
+        <v>723.8398581678547</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>754.7825099294947</v>
+        <v>754.7825099294945</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>618.0593823539726</v>
+        <v>618.0593823539725</v>
       </c>
       <c r="I12" s="162" t="n">
         <v>649.6781087871136</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>689.6675854315775</v>
+        <v>689.6675854315777</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>721.9945810099119</v>
+        <v>721.9945810099118</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>754.3659529910042</v>
+        <v>754.365952991004</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>89206779.15589008</v>
+        <v>89206779.15589009</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>99862129.38298918</v>
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>648.7478716827274</v>
+        <v>648.7478716827275</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>680.5931775077805</v>
@@ -2520,28 +2520,28 @@
         <v>721.1693203275079</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>753.6214082301321</v>
+        <v>753.6214082301319</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>786.0160670297594</v>
+        <v>786.0160670297591</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>643.7339395416344</v>
+        <v>643.7339395416345</v>
       </c>
       <c r="Z12" s="162" t="n">
         <v>676.6299722545758</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>718.267648642198</v>
+        <v>718.2676486421981</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>751.9235017689936</v>
+        <v>751.9235017689933</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>785.6177422864325</v>
+        <v>785.6177422864322</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>89206779.15589008</v>
+        <v>89206779.15589009</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>99862129.38298918</v>
@@ -2603,49 +2603,49 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>6677.893717226249</v>
+        <v>6677.893717226247</v>
       </c>
       <c r="D13" s="156" t="n">
         <v>6796.199828393555</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>7104.168020114192</v>
+        <v>7104.168020114186</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>7243.760854401225</v>
+        <v>7243.760854401222</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>7504.875527837429</v>
+        <v>7504.875527837425</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>6677.25407774167</v>
+        <v>6677.254077741668</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>6795.602709658776</v>
+        <v>6795.602709658774</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>7103.58883269225</v>
+        <v>7103.588832692245</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>7243.225595014702</v>
+        <v>7243.225595014699</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>7504.378226816275</v>
+        <v>7504.378226816271</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>62846962.67245872</v>
+        <v>62846962.67245871</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>71540911.47072142</v>
+        <v>71540911.47072141</v>
       </c>
       <c r="O13" s="159" t="n">
-        <v>83041387.84785938</v>
+        <v>83041387.84785932</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>95317771.45889692</v>
+        <v>95317771.45889689</v>
       </c>
       <c r="Q13" s="160" t="n">
-        <v>112357039.2962068</v>
+        <v>112357039.2962067</v>
       </c>
       <c r="S13" s="32" t="inlineStr">
         <is>
@@ -2656,46 +2656,46 @@
         <v>4080.111470312186</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>4152.395058764123</v>
+        <v>4152.395058764122</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>4340.559861131266</v>
+        <v>4340.559861131264</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4425.849377326875</v>
+        <v>4425.849377326873</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4585.387252481378</v>
+        <v>4585.387252481375</v>
       </c>
       <c r="Y13" s="155" t="n">
         <v>4079.827928150462</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>4152.130365960325</v>
+        <v>4152.130365960324</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4340.303117426539</v>
+        <v>4340.303117426535</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4425.612106653087</v>
+        <v>4425.612106653085</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>4585.166808516748</v>
+        <v>4585.166808516746</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>62846962.67245872</v>
+        <v>62846962.67245871</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>71540911.47072142</v>
+        <v>71540911.47072141</v>
       </c>
       <c r="AF13" s="159" t="n">
-        <v>83041387.84785938</v>
+        <v>83041387.84785932</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>95317771.45889692</v>
+        <v>95317771.45889689</v>
       </c>
       <c r="AH13" s="160" t="n">
-        <v>112357039.2962068</v>
+        <v>112357039.2962067</v>
       </c>
       <c r="AJ13" s="39" t="n"/>
       <c r="AQ13" s="49" t="inlineStr">
@@ -2746,28 +2746,28 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>997.2387216279361</v>
+        <v>997.2387216279359</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>1050.145387191724</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>1122.096443479686</v>
+        <v>1122.096443479685</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>1176.749953779059</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>1235.525193640785</v>
+        <v>1235.525193640784</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>988.9946533044891</v>
+        <v>988.9946533044889</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>1043.627899833212</v>
+        <v>1043.627899833211</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>1117.302893604357</v>
+        <v>1117.302893604356</v>
       </c>
       <c r="K14" s="168" t="n">
         <v>1173.951959467463</v>
@@ -2782,13 +2782,13 @@
         <v>171403040.8537106</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>195901505.5484629</v>
+        <v>195901505.5484628</v>
       </c>
       <c r="P14" s="171" t="n">
         <v>222907303.1726156</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>259720046.8546799</v>
+        <v>259720046.8546798</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>1045.415172627005</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>1115.43754974965</v>
+        <v>1115.437549749649</v>
       </c>
       <c r="W14" s="168" t="n">
         <v>1168.041584907186</v>
@@ -2823,7 +2823,7 @@
         <v>1165.699340627499</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>1224.629967252641</v>
+        <v>1224.62996725264</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>152053741.8283488</v>
@@ -2832,13 +2832,13 @@
         <v>171403040.8537106</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>195901505.5484629</v>
+        <v>195901505.5484628</v>
       </c>
       <c r="AG14" s="171" t="n">
         <v>222907303.1726156</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>259720046.8546799</v>
+        <v>259720046.8546798</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>176267.6236656359</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>195239.0332577241</v>
+        <v>195239.0332577242</v>
       </c>
       <c r="H23" s="85" t="n">
         <v>1270.098661326248</v>
@@ -3771,7 +3771,7 @@
         <v>1071.011065912703</v>
       </c>
       <c r="Z23" s="86" t="n">
-        <v>859.4261510053072</v>
+        <v>859.4261510053074</v>
       </c>
       <c r="AA23" s="86" t="n">
         <v>632.2156204549408</v>
@@ -3966,7 +3966,7 @@
         <v>749.020863243838</v>
       </c>
       <c r="K25" s="92" t="n">
-        <v>451.4780180637046</v>
+        <v>451.4780180637045</v>
       </c>
       <c r="L25" s="93" t="n">
         <v>108.8020879108765</v>
@@ -3984,7 +3984,7 @@
         <v>189877.7044281543</v>
       </c>
       <c r="Q25" s="93" t="n">
-        <v>210319.0415807613</v>
+        <v>210319.0415807614</v>
       </c>
       <c r="S25" s="51" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>175627.4975613213</v>
       </c>
       <c r="W25" s="92" t="n">
-        <v>190838.4992905266</v>
+        <v>190838.4992905267</v>
       </c>
       <c r="X25" s="93" t="n">
         <v>211984.1925639558</v>
@@ -4010,7 +4010,7 @@
         <v>1072.081569346541</v>
       </c>
       <c r="Z25" s="92" t="n">
-        <v>860.5244661116376</v>
+        <v>860.5244661116377</v>
       </c>
       <c r="AA25" s="92" t="n">
         <v>633.3473133561454</v>
@@ -4019,7 +4019,7 @@
         <v>383.4525488077977</v>
       </c>
       <c r="AC25" s="93" t="n">
-        <v>96.23483023983755</v>
+        <v>96.23483023983754</v>
       </c>
       <c r="AD25" s="91" t="n">
         <v>153981.4117751766</v>
@@ -4031,10 +4031,10 @@
         <v>176260.8448746775</v>
       </c>
       <c r="AG25" s="92" t="n">
-        <v>191221.9518393344</v>
+        <v>191221.9518393345</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>212080.4273941956</v>
+        <v>212080.4273941957</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4420,7 +4420,7 @@
         <v>607.8228420888065</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>638.5852069001241</v>
+        <v>638.5852069001239</v>
       </c>
       <c r="H35" s="148" t="n">
         <v>487.8118631917249</v>
@@ -4435,7 +4435,7 @@
         <v>606.2810824536837</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>638.3128521848377</v>
+        <v>638.3128521848374</v>
       </c>
       <c r="M35" s="151" t="n">
         <v>54387880.6634843</v>
@@ -4450,7 +4450,7 @@
         <v>83444510.22674274</v>
       </c>
       <c r="Q35" s="153" t="n">
-        <v>97058201.90610689</v>
+        <v>97058201.90610687</v>
       </c>
       <c r="S35" s="21" t="inlineStr">
         <is>
@@ -4470,7 +4470,7 @@
         <v>629.294643984629</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>661.1437126137988</v>
+        <v>661.1437126137986</v>
       </c>
       <c r="Y35" s="148" t="n">
         <v>505.7948878959876</v>
@@ -4485,7 +4485,7 @@
         <v>627.9627012595671</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>660.9085048258072</v>
+        <v>660.908504825807</v>
       </c>
       <c r="AD35" s="151" t="n">
         <v>54387880.6634843</v>
@@ -4500,7 +4500,7 @@
         <v>83444510.22674274</v>
       </c>
       <c r="AH35" s="153" t="n">
-        <v>97058201.90610689</v>
+        <v>97058201.90610687</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickBot="1">
@@ -4624,7 +4624,7 @@
         <v>731.7200398084702</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>765.7813492471375</v>
+        <v>765.7813492471373</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>598.1882449500856</v>
@@ -4639,7 +4639,7 @@
         <v>729.7326648377847</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>765.3303669677167</v>
+        <v>765.3303669677166</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>81320787.17092901</v>
@@ -4674,7 +4674,7 @@
         <v>754.6517235925378</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>789.7951397662774</v>
+        <v>789.7951397662771</v>
       </c>
       <c r="Y37" s="161" t="n">
         <v>617.5375254445779</v>
@@ -4689,7 +4689,7 @@
         <v>752.857270964295</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>789.3721536446168</v>
+        <v>789.3721536446166</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>81320787.17092901</v>
@@ -4717,7 +4717,7 @@
         <v>1246.939969245402</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>1329.58625847311</v>
+        <v>1329.586258473111</v>
       </c>
       <c r="E38" s="156" t="n">
         <v>1400.756957322541</v>
@@ -4747,7 +4747,7 @@
         <v>10412897.97111799</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>11976639.76851665</v>
+        <v>11976639.76851666</v>
       </c>
       <c r="O38" s="159" t="n">
         <v>13722222.93853281</v>
@@ -4767,7 +4767,7 @@
         <v>1518.32098018215</v>
       </c>
       <c r="U38" s="156" t="n">
-        <v>1618.954208696405</v>
+        <v>1618.954208696406</v>
       </c>
       <c r="V38" s="156" t="n">
         <v>1705.614326987994</v>
@@ -4776,13 +4776,13 @@
         <v>1775.677662513187</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>1820.663576343646</v>
+        <v>1820.663576343645</v>
       </c>
       <c r="Y38" s="155" t="n">
         <v>1510.973741075437</v>
       </c>
       <c r="Z38" s="156" t="n">
-        <v>1614.238553625912</v>
+        <v>1614.238553625913</v>
       </c>
       <c r="AA38" s="156" t="n">
         <v>1703.854573768357</v>
@@ -4791,13 +4791,13 @@
         <v>1775.677662513187</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>1820.663576343646</v>
+        <v>1820.663576343645</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>10412897.97111799</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>11976639.76851665</v>
+        <v>11976639.76851666</v>
       </c>
       <c r="AF38" s="159" t="n">
         <v>13722222.93853281</v>
@@ -4825,10 +4825,10 @@
         <v>733.8712476733501</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>776.4400875106124</v>
+        <v>776.4400875106122</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>811.6710334172313</v>
+        <v>811.6710334172309</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>635.566773247903</v>
@@ -4840,13 +4840,13 @@
         <v>730.5164977740903</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>774.4607171542729</v>
+        <v>774.4607171542727</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>811.2230802700748</v>
+        <v>811.2230802700743</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>91733685.14204699</v>
+        <v>91733685.142047</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>105105908.6458666</v>
@@ -4855,7 +4855,7 @@
         <v>119544806.313354</v>
       </c>
       <c r="P39" s="165" t="n">
-        <v>136861249.1442341</v>
+        <v>136861249.144234</v>
       </c>
       <c r="Q39" s="166" t="n">
         <v>158469867.8876781</v>
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>667.1245566832798</v>
+        <v>667.1245566832799</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>716.3312537206747</v>
@@ -4875,28 +4875,28 @@
         <v>763.884075917671</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>808.3858129022556</v>
+        <v>808.3858129022553</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>845.2586871258951</v>
+        <v>845.2586871258948</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>661.9685979466591</v>
+        <v>661.9685979466592</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>712.1599398115693</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>760.8105386338848</v>
+        <v>760.8105386338849</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>806.5645224242649</v>
+        <v>806.5645224242646</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>844.8303403481167</v>
+        <v>844.8303403481164</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>91733685.14204699</v>
+        <v>91733685.142047</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>105105908.6458666</v>
@@ -4905,7 +4905,7 @@
         <v>119544806.313354</v>
       </c>
       <c r="AG39" s="165" t="n">
-        <v>136861249.1442341</v>
+        <v>136861249.144234</v>
       </c>
       <c r="AH39" s="166" t="n">
         <v>158469867.8876781</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>6868.84768280832</v>
+        <v>6868.847682808318</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>7154.64767701185</v>
+        <v>7154.647677011848</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>7527.196461235634</v>
+        <v>7527.196461235629</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>7772.2755948511</v>
+        <v>7772.275594851097</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>8072.362620025201</v>
+        <v>8072.362620025197</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>6868.189752871498</v>
+        <v>6868.189752871496</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>7154.019064805533</v>
+        <v>7154.019064805531</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>7526.582785221711</v>
+        <v>7526.582785221705</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>7771.701282204616</v>
+        <v>7771.701282204614</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>8071.827715194445</v>
+        <v>8071.82771519444</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>64644067.75607768</v>
+        <v>64644067.75607767</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>75314150.4060653</v>
+        <v>75314150.40606529</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>87986213.01955858</v>
+        <v>87986213.01955852</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>102272286.9730654</v>
+        <v>102272286.9730653</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>120853005.5891221</v>
+        <v>120853005.589122</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>4196.782010195625</v>
+        <v>4196.782010195624</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4371.402314732207</v>
+        <v>4371.402314732206</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>4599.025070069153</v>
+        <v>4599.02507006915</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>4748.765426316389</v>
+        <v>4748.765426316388</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>4932.114932216175</v>
+        <v>4932.114932216172</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>4196.490360162994</v>
+        <v>4196.490360162993</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4371.123661396278</v>
+        <v>4371.123661396277</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4598.753038171793</v>
+        <v>4598.75303817179</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>4748.510844048376</v>
+        <v>4748.510844048375</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>4931.877819207</v>
+        <v>4931.877819206998</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>64644067.75607768</v>
+        <v>64644067.75607767</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>75314150.4060653</v>
+        <v>75314150.40606529</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>87986213.01955858</v>
+        <v>87986213.01955852</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>102272286.9730654</v>
+        <v>102272286.9730653</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>120853005.5891221</v>
+        <v>120853005.589122</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5029,10 +5029,10 @@
         <v>1188.708673030422</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1262.409860816195</v>
+        <v>1262.409860816194</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>1328.778627295653</v>
+        <v>1328.778627295652</v>
       </c>
       <c r="H41" s="179" t="n">
         <v>1017.119076797239</v>
@@ -5041,13 +5041,13 @@
         <v>1098.530144963152</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>1183.63055844899</v>
+        <v>1183.630558448989</v>
       </c>
       <c r="K41" s="180" t="n">
         <v>1259.408190326961</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>1328.091224538706</v>
+        <v>1328.091224538704</v>
       </c>
       <c r="M41" s="182" t="n">
         <v>156377752.8981247</v>
@@ -5059,10 +5059,10 @@
         <v>207531019.3329126</v>
       </c>
       <c r="P41" s="183" t="n">
-        <v>239133536.1172994</v>
+        <v>239133536.1172993</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>279322873.4768002</v>
+        <v>279322873.4768001</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5076,13 +5076,13 @@
         <v>1100.411441008963</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1181.654480161639</v>
+        <v>1181.654480161638</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1253.067578116143</v>
+        <v>1253.067578116142</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1317.658973050683</v>
+        <v>1317.658973050682</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>1015.562535083435</v>
@@ -5094,7 +5094,7 @@
         <v>1177.408513390869</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>1250.554833360453</v>
+        <v>1250.554833360452</v>
       </c>
       <c r="AC41" s="187" t="n">
         <v>1317.061064563117</v>
@@ -5109,10 +5109,10 @@
         <v>207531019.3329126</v>
       </c>
       <c r="AG41" s="189" t="n">
-        <v>239133536.1172994</v>
+        <v>239133536.1172993</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>279322873.4768002</v>
+        <v>279322873.4768001</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5383,7 +5383,7 @@
         <v>0.2216682562048453</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2388240245289702</v>
+        <v>0.2388240245289701</v>
       </c>
       <c r="H46" s="148" t="n">
         <v>0.1641628339753153</v>
@@ -5424,7 +5424,7 @@
         <v>0.1714961154068534</v>
       </c>
       <c r="U46" s="149" t="n">
-        <v>0.1885209395901673</v>
+        <v>0.1885209395901672</v>
       </c>
       <c r="V46" s="149" t="n">
         <v>0.2089394933442075</v>
@@ -5433,16 +5433,16 @@
         <v>0.2294988551133468</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2472606639369704</v>
+        <v>0.2472606639369703</v>
       </c>
       <c r="Y46" s="148" t="n">
         <v>0.1702146431289184</v>
       </c>
       <c r="Z46" s="149" t="n">
-        <v>0.1874674454598498</v>
+        <v>0.1874674454598497</v>
       </c>
       <c r="AA46" s="149" t="n">
-        <v>0.2081356546843188</v>
+        <v>0.2081356546843187</v>
       </c>
       <c r="AB46" s="149" t="n">
         <v>0.229013105975959</v>
@@ -5578,7 +5578,7 @@
         <v>0.1408879555542316</v>
       </c>
       <c r="D48" s="162" t="n">
-        <v>0.1552744269920273</v>
+        <v>0.1552744269920272</v>
       </c>
       <c r="E48" s="162" t="n">
         <v>0.1720533945320395</v>
@@ -5631,13 +5631,13 @@
         <v>0.1601263113495038</v>
       </c>
       <c r="V48" s="162" t="n">
-        <v>0.1774417726621427</v>
+        <v>0.1774417726621426</v>
       </c>
       <c r="W48" s="162" t="n">
         <v>0.1944502457929139</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.2090592132788226</v>
+        <v>0.2090592132788225</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.1441267332446844</v>
@@ -5652,7 +5652,7 @@
         <v>0.1939878712382459</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.2089472486168871</v>
+        <v>0.208947248616887</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>18979.4124517282</v>
@@ -5683,7 +5683,7 @@
         <v>0.1603913353814516</v>
       </c>
       <c r="E49" s="156" t="n">
-        <v>0.161939716471679</v>
+        <v>0.1619397164716791</v>
       </c>
       <c r="F49" s="156" t="n">
         <v>0.1614433720814726</v>
@@ -5695,10 +5695,10 @@
         <v>0.1580143047503502</v>
       </c>
       <c r="I49" s="156" t="n">
-        <v>0.1599567521247956</v>
+        <v>0.1599567521247957</v>
       </c>
       <c r="J49" s="156" t="n">
-        <v>0.1617843162051968</v>
+        <v>0.1617843162051969</v>
       </c>
       <c r="K49" s="156" t="n">
         <v>0.1614433720814726</v>
@@ -5748,7 +5748,7 @@
         <v>0.1947296578844112</v>
       </c>
       <c r="AA49" s="156" t="n">
-        <v>0.1969804434256948</v>
+        <v>0.1969804434256949</v>
       </c>
       <c r="AB49" s="156" t="n">
         <v>0.1965795186523627</v>
@@ -5779,25 +5779,25 @@
         </is>
       </c>
       <c r="C50" s="161" t="n">
-        <v>0.1419293489758365</v>
+        <v>0.1419293489758364</v>
       </c>
       <c r="D50" s="162" t="n">
         <v>0.1555762903749652</v>
       </c>
       <c r="E50" s="162" t="n">
-        <v>0.1714451755531917</v>
+        <v>0.1714451755531916</v>
       </c>
       <c r="F50" s="162" t="n">
         <v>0.1868736067437889</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.1999099918541769</v>
+        <v>0.1999099918541768</v>
       </c>
       <c r="H50" s="161" t="n">
-        <v>0.1406804077157211</v>
+        <v>0.140680407715721</v>
       </c>
       <c r="I50" s="162" t="n">
-        <v>0.1545455479351502</v>
+        <v>0.1545455479351501</v>
       </c>
       <c r="J50" s="162" t="n">
         <v>0.1706614472258602</v>
@@ -5806,13 +5806,13 @@
         <v>0.1863972118699012</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.1997996635237176</v>
+        <v>0.1997996635237175</v>
       </c>
       <c r="M50" s="164" t="n">
         <v>20304.91959342107</v>
       </c>
       <c r="N50" s="165" t="n">
-        <v>23755.22169321252</v>
+        <v>23755.22169321251</v>
       </c>
       <c r="O50" s="165" t="n">
         <v>27927.7603119667</v>
@@ -5841,7 +5841,7 @@
         <v>0.194562304197733</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.2081824412860989</v>
+        <v>0.2081824412860988</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.1465243561714898</v>
@@ -5856,13 +5856,13 @@
         <v>0.194123955990286</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.2080769418936961</v>
+        <v>0.208076941893696</v>
       </c>
       <c r="AD50" s="164" t="n">
         <v>20304.91959342107</v>
       </c>
       <c r="AE50" s="165" t="n">
-        <v>23755.22169321252</v>
+        <v>23755.22169321251</v>
       </c>
       <c r="AF50" s="165" t="n">
         <v>27927.7603119667</v>
@@ -6004,7 +6004,7 @@
         <v>0.1446392782898112</v>
       </c>
       <c r="J52" s="180" t="n">
-        <v>0.1592829382351531</v>
+        <v>0.159282938235153</v>
       </c>
       <c r="K52" s="180" t="n">
         <v>0.1734788541169557</v>
@@ -6016,7 +6016,7 @@
         <v>20304.91959342107</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>23755.22169321252</v>
+        <v>23755.22169321251</v>
       </c>
       <c r="O52" s="183" t="n">
         <v>27927.7603119667</v>
@@ -6045,7 +6045,7 @@
         <v>0.1726054580653966</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.1841186037321795</v>
+        <v>0.1841186037321794</v>
       </c>
       <c r="Y52" s="185" t="n">
         <v>0.1318660438252615</v>
@@ -6066,7 +6066,7 @@
         <v>20304.91959342107</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>23755.22169321252</v>
+        <v>23755.22169321251</v>
       </c>
       <c r="AF52" s="189" t="n">
         <v>27927.7603119667</v>
@@ -6334,46 +6334,46 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.009417356194386618</v>
+        <v>0.009417356194386627</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0.008600077056639933</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007897561678242916</v>
+        <v>0.007897561678242907</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0002850966978455693</v>
+        <v>0.0002850966978455694</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.009333113971321931</v>
+        <v>0.009333113971321938</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.008542522022148063</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.007861161786416167</v>
+        <v>0.007861161786416158</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.0002843735420995058</v>
+        <v>0.0002843735420995059</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1040.582091566415</v>
+        <v>1040.582091566416</v>
       </c>
       <c r="N57" s="152" t="n">
         <v>1020.643796130887</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>39.13928972664269</v>
+        <v>39.13928972664271</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6384,46 +6384,46 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.009750031428988485</v>
+        <v>0.009750031428988492</v>
       </c>
       <c r="U57" s="149" t="n">
         <v>0.008903881287185783</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008176549021384745</v>
+        <v>0.008176549021384736</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0002951679544575392</v>
+        <v>0.0002951679544575393</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.009677176163692222</v>
+        <v>0.009677176163692231</v>
       </c>
       <c r="Z57" s="149" t="n">
         <v>0.008854124550912952</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.008145091942099898</v>
+        <v>0.00814509194209989</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.0002945432124334822</v>
+        <v>0.0002945432124334823</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1040.582091566415</v>
+        <v>1040.582091566416</v>
       </c>
       <c r="AE57" s="152" t="n">
         <v>1020.643796130887</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>39.13928972664269</v>
+        <v>39.13928972664271</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,46 +6538,46 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.007724447942738561</v>
+        <v>0.007724447942738568</v>
       </c>
       <c r="D59" s="162" t="n">
         <v>0.007103392540783734</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006547122336295315</v>
+        <v>0.006547122336295307</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002366076333979678</v>
+        <v>0.0002366076333979679</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.00765442633717059</v>
+        <v>0.007654426337170597</v>
       </c>
       <c r="I59" s="162" t="n">
         <v>0.007054593779841191</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006515686226430602</v>
+        <v>0.006515686226430595</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.0002359649995176502</v>
+        <v>0.0002359649995176503</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1040.582091566415</v>
+        <v>1040.582091566416</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>1020.643796130887</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>39.13928972664269</v>
+        <v>39.13928972664271</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,13 +6588,13 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.007964781323230708</v>
+        <v>0.007964781323230715</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.007325353360870443</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.00675216549111336</v>
+        <v>0.006752165491113352</v>
       </c>
       <c r="W59" s="162" t="n">
         <v>0.0002440227800863092</v>
@@ -6603,31 +6603,31 @@
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.007902020039441857</v>
+        <v>0.007902020039441864</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0.007281568143488029</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.006723906355547833</v>
+        <v>0.006723906355547826</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.0002434425292164212</v>
+        <v>0.0002434425292164213</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1040.582091566415</v>
+        <v>1040.582091566416</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>1020.643796130887</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>39.13928972664269</v>
+        <v>39.13928972664271</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,13 +6742,13 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.007273564326735271</v>
+        <v>0.007273564326735277</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0.006684339874699444</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.006153389805161951</v>
+        <v>0.006153389805161944</v>
       </c>
       <c r="F61" s="162" t="n">
         <v>0.0002220446892781993</v>
@@ -6757,31 +6757,31 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.007209558857385097</v>
+        <v>0.007209558857385103</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.006640053995569693</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.006125260778586213</v>
+        <v>0.006125260778586206</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.0002214786331422403</v>
+        <v>0.0002214786331422404</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1040.582091566415</v>
+        <v>1040.582091566416</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>1020.643796130887</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>39.13928972664269</v>
+        <v>39.13928972664271</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,46 +6792,46 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.007567534929550245</v>
+        <v>0.007567534929550251</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.006956022354062191</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.006405042437593305</v>
+        <v>0.006405042437593297</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002311804600639357</v>
+        <v>0.0002311804600639358</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.007509048253495804</v>
+        <v>0.007509048253495811</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0.00691551629957017</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006379271332582997</v>
+        <v>0.00637927133258299</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.0002306596112762753</v>
+        <v>0.0002306596112762754</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1040.582091566415</v>
+        <v>1040.582091566416</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>1020.643796130887</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>39.13928972664269</v>
+        <v>39.13928972664271</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,46 +6946,46 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006824618337338056</v>
+        <v>0.006824618337338061</v>
       </c>
       <c r="D63" s="180" t="n">
         <v>0.006253240135847324</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005741398344689726</v>
+        <v>0.005741398344689719</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002066202260816287</v>
+        <v>0.0002066202260816288</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.006768199930557162</v>
+        <v>0.006768199930557167</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.006214430829981478</v>
+        <v>0.006214430829981477</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.005716871326999468</v>
+        <v>0.005716871326999462</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.0002061289388583912</v>
+        <v>0.0002061289388583913</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1040.582091566415</v>
+        <v>1040.582091566416</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>1020.643796130887</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>39.13928972664269</v>
+        <v>39.13928972664271</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6996,46 +6996,46 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.006805223004807462</v>
+        <v>0.006805223004807468</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0.006225073400147639</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.005707326976171228</v>
+        <v>0.005707326976171222</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.000205091162800742</v>
+        <v>0.0002050911628007421</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.006757842258815865</v>
+        <v>0.006757842258815871</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0.006192571814392445</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.005686819187221429</v>
+        <v>0.005686819187221422</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.0002046798986735984</v>
+        <v>0.0002046798986735985</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1040.582091566415</v>
+        <v>1040.582091566416</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>1020.643796130887</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1002.363554589176</v>
+        <v>1002.363554589175</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>39.13928972664269</v>
+        <v>39.13928972664271</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7297,43 +7297,43 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.003997120704944832</v>
+        <v>0.003997120704944835</v>
       </c>
       <c r="D68" s="149" t="n">
         <v>0.005764545014327062</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.007564491641164404</v>
+        <v>0.007564491641164398</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.009173087327773003</v>
+        <v>0.009173087327773007</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.01054079156232654</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.003961364774395752</v>
+        <v>0.003961364774395754</v>
       </c>
       <c r="I68" s="149" t="n">
         <v>0.005725966454513651</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.007529626870405945</v>
+        <v>0.007529626870405939</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.009149819535264885</v>
+        <v>0.009149819535264888</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.01053629594568239</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>441.6666564947561</v>
+        <v>441.6666564947564</v>
       </c>
       <c r="N68" s="152" t="n">
         <v>684.1272546328629</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>960.0900935014438</v>
+        <v>960.090093501443</v>
       </c>
       <c r="P68" s="152" t="n">
         <v>1259.32052290546</v>
@@ -7347,43 +7347,43 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004138322018859465</v>
+        <v>0.004138322018859468</v>
       </c>
       <c r="U68" s="149" t="n">
         <v>0.005968181929553585</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.007831713033179739</v>
+        <v>0.007831713033179732</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.009497133579799585</v>
+        <v>0.009497133579799588</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01091315300151439</v>
+        <v>0.01091315300151438</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.004107399190480782</v>
+        <v>0.004107399190480786</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>0.005934830490476735</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.007801582617869248</v>
+        <v>0.007801582617869241</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.009477032283687384</v>
+        <v>0.009477032283687388</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.01090927054974403</v>
+        <v>0.01090927054974402</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>441.6666564947561</v>
+        <v>441.6666564947564</v>
       </c>
       <c r="AE68" s="152" t="n">
         <v>684.1272546328629</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>960.0900935014438</v>
+        <v>960.090093501443</v>
       </c>
       <c r="AG68" s="152" t="n">
         <v>1259.32052290546</v>
@@ -7501,43 +7501,43 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003278579483336601</v>
+        <v>0.003278579483336603</v>
       </c>
       <c r="D70" s="162" t="n">
         <v>0.004761332460872311</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.006271005432350781</v>
+        <v>0.006271005432350775</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007612934488469347</v>
+        <v>0.00761293448846935</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.008756654254511649</v>
+        <v>0.008756654254511647</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.003248859378921728</v>
+        <v>0.003248859378921731</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.00472862314300876</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.006240895102100691</v>
+        <v>0.006240895102100686</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.007592257515538809</v>
+        <v>0.007592257515538811</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.008751497304816174</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>441.6666564947561</v>
+        <v>441.6666564947564</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>684.1272546328629</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>960.0900935014438</v>
+        <v>960.090093501443</v>
       </c>
       <c r="P70" s="165" t="n">
         <v>1259.32052290546</v>
@@ -7551,43 +7551,43 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003380587043784102</v>
+        <v>0.003380587043784105</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>0.004910110562554425</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.006467401142050913</v>
+        <v>0.006467401142050908</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.007851519462039427</v>
+        <v>0.007851519462039429</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.009031250209509914</v>
+        <v>0.009031250209509911</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.003353948524254506</v>
+        <v>0.003353948524254508</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.004880761772433044</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.006440333801081501</v>
+        <v>0.006440333801081496</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.007832849684585948</v>
+        <v>0.007832849684585952</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.009026413393850352</v>
+        <v>0.00902641339385035</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>441.6666564947561</v>
+        <v>441.6666564947564</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>684.1272546328629</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>960.0900935014438</v>
+        <v>960.090093501443</v>
       </c>
       <c r="AG70" s="165" t="n">
         <v>1259.32052290546</v>
@@ -7603,25 +7603,25 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.008933636187012022</v>
+        <v>0.008933636187012026</v>
       </c>
       <c r="D71" s="156" t="n">
         <v>0.01300501029810884</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.01704301169374894</v>
+        <v>0.01704301169374895</v>
       </c>
       <c r="F71" s="156" t="n">
         <v>0.02060031929126705</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.02351505810183461</v>
+        <v>0.0235150581018346</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.008893417117733135</v>
+        <v>0.008893417117733138</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.01296977298485401</v>
+        <v>0.01296977298485402</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.01702665691299119</v>
@@ -7630,22 +7630,22 @@
         <v>0.02060031929126705</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.02351505810183461</v>
+        <v>0.0235150581018346</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>74.60266285532474</v>
+        <v>74.60266285532477</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>117.1464600613191</v>
       </c>
       <c r="O71" s="159" t="n">
-        <v>166.9583040677297</v>
+        <v>166.9583040677298</v>
       </c>
       <c r="P71" s="159" t="n">
         <v>223.4945477325937</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>288.8188648367187</v>
+        <v>288.8188648367186</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>0.01583538940936581</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.02075221170091156</v>
+        <v>0.02075221170091157</v>
       </c>
       <c r="W71" s="156" t="n">
         <v>0.02508372315413866</v>
@@ -7671,10 +7671,10 @@
         <v>0.01082529233469451</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.01578926442697879</v>
+        <v>0.0157892644269788</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.02073080078123445</v>
+        <v>0.02073080078123446</v>
       </c>
       <c r="AB71" s="156" t="n">
         <v>0.02508372315413866</v>
@@ -7683,19 +7683,19 @@
         <v>0.02863281869761861</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>74.60266285532474</v>
+        <v>74.60266285532477</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>117.1464600613191</v>
       </c>
       <c r="AF71" s="159" t="n">
-        <v>166.9583040677297</v>
+        <v>166.9583040677298</v>
       </c>
       <c r="AG71" s="159" t="n">
         <v>223.4945477325937</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>288.8188648367187</v>
+        <v>288.8188648367186</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,37 +7705,37 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.00360867069945435</v>
+        <v>0.003608670699454353</v>
       </c>
       <c r="D72" s="162" t="n">
         <v>0.005247654335413232</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.006918815122292312</v>
+        <v>0.006918815122292307</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008412293986845946</v>
+        <v>0.00841229398684595</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.009685090832465255</v>
+        <v>0.009685090832465252</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.003576915338331083</v>
+        <v>0.003576915338331085</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.005212886955242683</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.006887187102516235</v>
+        <v>0.00688718710251623</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.008390848616347675</v>
+        <v>0.008390848616347677</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.009679745727440828</v>
+        <v>0.009679745727440825</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>516.2693193500808</v>
+        <v>516.2693193500812</v>
       </c>
       <c r="N72" s="165" t="n">
         <v>801.273714694182</v>
@@ -7755,37 +7755,37 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.003754519839329282</v>
+        <v>0.003754519839329286</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.005460943271554864</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.007201771036668175</v>
+        <v>0.007201771036668171</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.008758408050172023</v>
+        <v>0.008758408050172025</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>0.0100858683194334</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.003725502545371992</v>
+        <v>0.003725502545371995</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.005429143306793931</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.007172794242298035</v>
+        <v>0.007172794242298031</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.008738675386721552</v>
+        <v>0.008738675386721554</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.01008075716321398</v>
+        <v>0.01008075716321397</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>516.2693193500808</v>
+        <v>516.2693193500812</v>
       </c>
       <c r="AE72" s="165" t="n">
         <v>801.273714694182</v>
@@ -7909,37 +7909,37 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.00338593282778663</v>
+        <v>0.003385932827786632</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.004909212177176243</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.006455575698620613</v>
+        <v>0.00645557569862061</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.007827929103269437</v>
+        <v>0.007827929103269439</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.008995317143949477</v>
+        <v>0.008995317143949475</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.003357941674850543</v>
+        <v>0.003357941674850545</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.004878744273688549</v>
+        <v>0.004878744273688548</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006427997744635361</v>
+        <v>0.006427997744635356</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.007809316397118754</v>
+        <v>0.007809316397118756</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.008990663693271278</v>
+        <v>0.008990663693271275</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>516.2693193500808</v>
+        <v>516.2693193500812</v>
       </c>
       <c r="N74" s="183" t="n">
         <v>801.273714694182</v>
@@ -7959,37 +7959,37 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003376310122182437</v>
+        <v>0.00337631012218244</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.004887099403816475</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.006417266164005201</v>
+        <v>0.006417266164005198</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.007769999639227207</v>
+        <v>0.007769999639227208</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.008920041387393897</v>
+        <v>0.008920041387393895</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.003352802870153374</v>
+        <v>0.003352802870153378</v>
       </c>
       <c r="Z74" s="186" t="n">
         <v>0.004861583482933754</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.006394207393993326</v>
+        <v>0.006394207393993322</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.007754418655259421</v>
+        <v>0.007754418655259422</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.008915993778290145</v>
+        <v>0.008915993778290143</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>516.2693193500808</v>
+        <v>516.2693193500812</v>
       </c>
       <c r="AE74" s="189" t="n">
         <v>801.273714694182</v>
@@ -8272,7 +8272,7 @@
         <v>608.053968529037</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>638.8345717162155</v>
+        <v>638.8345717162152</v>
       </c>
       <c r="H79" s="148" t="n">
         <v>487.989320504446</v>
@@ -8287,7 +8287,7 @@
         <v>606.5116226352355</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>638.5621106475672</v>
+        <v>638.562110647567</v>
       </c>
       <c r="M79" s="151" t="n">
         <v>54407666.01081879</v>
@@ -8302,7 +8302,7 @@
         <v>83476240.2494895</v>
       </c>
       <c r="Q79" s="153" t="n">
-        <v>97096102.72248495</v>
+        <v>97096102.72248493</v>
       </c>
       <c r="S79" s="21" t="inlineStr">
         <is>
@@ -8322,7 +8322,7 @@
         <v>629.5339351412766</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>661.4018864307372</v>
+        <v>661.401886430737</v>
       </c>
       <c r="Y79" s="148" t="n">
         <v>505.9788871144708</v>
@@ -8337,7 +8337,7 @@
         <v>628.2014859410391</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>661.1665867951016</v>
+        <v>661.1665867951014</v>
       </c>
       <c r="AD79" s="151" t="n">
         <v>54407666.01081879</v>
@@ -8352,7 +8352,7 @@
         <v>83476240.2494895</v>
       </c>
       <c r="AH79" s="153" t="n">
-        <v>97096102.72248495</v>
+        <v>97096102.72248493</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" thickBot="1">
@@ -8476,7 +8476,7 @@
         <v>731.9164308156736</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>765.9928086509489</v>
+        <v>765.9928086509486</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>598.3387590514326</v>
@@ -8491,7 +8491,7 @@
         <v>729.9285224407473</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>765.5417018393179</v>
+        <v>765.5417018393177</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>81341248.83212879</v>
@@ -8526,7 +8526,7 @@
         <v>754.8542693805729</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>790.0132302297658</v>
+        <v>790.0132302297654</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>617.6929081463862</v>
@@ -8541,7 +8541,7 @@
         <v>753.059335127747</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>789.5901273066276</v>
+        <v>789.5901273066273</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>81341248.83212879</v>
@@ -8593,7 +8593,7 @@
         <v>1458.479385810897</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1495.424406980468</v>
+        <v>1495.424406980467</v>
       </c>
       <c r="M82" s="158" t="n">
         <v>10414298.08092253</v>
@@ -8608,7 +8608,7 @@
         <v>15823162.0636725</v>
       </c>
       <c r="Q82" s="160" t="n">
-        <v>18367242.71753023</v>
+        <v>18367242.71753022</v>
       </c>
       <c r="S82" s="32" t="inlineStr">
         <is>
@@ -8619,7 +8619,7 @@
         <v>1518.525132388068</v>
       </c>
       <c r="U82" s="156" t="n">
-        <v>1619.165342605034</v>
+        <v>1619.165342605035</v>
       </c>
       <c r="V82" s="156" t="n">
         <v>1705.832263085935</v>
@@ -8628,7 +8628,7 @@
         <v>1775.899325754994</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1820.884972328644</v>
+        <v>1820.884972328643</v>
       </c>
       <c r="Y82" s="155" t="n">
         <v>1511.176905377552</v>
@@ -8643,7 +8643,7 @@
         <v>1775.899325754994</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1820.884972328644</v>
+        <v>1820.884972328643</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>10414298.08092253</v>
@@ -8658,7 +8658,7 @@
         <v>15823162.0636725</v>
       </c>
       <c r="AH82" s="160" t="n">
-        <v>18367242.71753023</v>
+        <v>18367242.71753022</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" thickTop="1">
@@ -8668,7 +8668,7 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>641.3620590012418</v>
+        <v>641.3620590012416</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>688.5208974801111</v>
@@ -8677,13 +8677,13 @@
         <v>734.0557650538308</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>776.6355954560321</v>
+        <v>776.6355954560322</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>811.880628499918</v>
+        <v>811.8806284999175</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>635.7182401298146</v>
+        <v>635.7182401298144</v>
       </c>
       <c r="I83" s="162" t="n">
         <v>683.9592273951524</v>
@@ -8692,13 +8692,13 @@
         <v>730.7001716691974</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>774.655726693392</v>
+        <v>774.6557266933922</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>811.4325596793259</v>
+        <v>811.4325596793254</v>
       </c>
       <c r="M83" s="164" t="n">
-        <v>91755546.91305134</v>
+        <v>91755546.91305132</v>
       </c>
       <c r="N83" s="165" t="n">
         <v>105131485.7850707</v>
@@ -8707,10 +8707,10 @@
         <v>119574863.4856182</v>
       </c>
       <c r="P83" s="165" t="n">
-        <v>136895710.8651809</v>
+        <v>136895710.865181</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>158510789.0289975</v>
+        <v>158510789.0289974</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>667.2835443470481</v>
+        <v>667.283544347048</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>716.5055703164652</v>
@@ -8727,13 +8727,13 @@
         <v>764.0761394289833</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>808.5893647949633</v>
+        <v>808.5893647949634</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>845.4769554355006</v>
+        <v>845.4769554355003</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>662.1263568536295</v>
+        <v>662.1263568536294</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>712.3332413333465</v>
@@ -8742,13 +8742,13 @@
         <v>761.0018293651622</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>806.7676157152529</v>
+        <v>806.767615715253</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>845.0484980471736</v>
+        <v>845.0484980471732</v>
       </c>
       <c r="AD83" s="164" t="n">
-        <v>91755546.91305134</v>
+        <v>91755546.91305132</v>
       </c>
       <c r="AE83" s="165" t="n">
         <v>105131485.7850707</v>
@@ -8757,10 +8757,10 @@
         <v>119574863.4856182</v>
       </c>
       <c r="AG83" s="165" t="n">
-        <v>136895710.8651809</v>
+        <v>136895710.865181</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>158510789.0289975</v>
+        <v>158510789.0289974</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>6868.84768280832</v>
+        <v>6868.847682808318</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>7154.64767701185</v>
+        <v>7154.647677011848</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>7527.196461235634</v>
+        <v>7527.196461235629</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>7772.2755948511</v>
+        <v>7772.275594851097</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>8072.362620025201</v>
+        <v>8072.362620025197</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>6868.189752871498</v>
+        <v>6868.189752871496</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>7154.019064805533</v>
+        <v>7154.019064805531</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>7526.582785221711</v>
+        <v>7526.582785221705</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>7771.701282204616</v>
+        <v>7771.701282204614</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>8071.827715194445</v>
+        <v>8071.82771519444</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>64644067.75607768</v>
+        <v>64644067.75607767</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>75314150.4060653</v>
+        <v>75314150.40606529</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>87986213.01955858</v>
+        <v>87986213.01955852</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>102272286.9730654</v>
+        <v>102272286.9730653</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>120853005.5891221</v>
+        <v>120853005.589122</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>4196.782010195625</v>
+        <v>4196.782010195624</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4371.402314732207</v>
+        <v>4371.402314732206</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>4599.025070069153</v>
+        <v>4599.02507006915</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>4748.765426316389</v>
+        <v>4748.765426316388</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>4932.114932216175</v>
+        <v>4932.114932216172</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>4196.490360162994</v>
+        <v>4196.490360162993</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4371.123661396278</v>
+        <v>4371.123661396277</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4598.753038171793</v>
+        <v>4598.75303817179</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>4748.510844048376</v>
+        <v>4748.510844048375</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>4931.877819207</v>
+        <v>4931.877819206998</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>64644067.75607768</v>
+        <v>64644067.75607767</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>75314150.4060653</v>
+        <v>75314150.40606529</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>87986213.01955858</v>
+        <v>87986213.01955852</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>102272286.9730654</v>
+        <v>102272286.9730653</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>120853005.5891221</v>
+        <v>120853005.589122</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8908,13 +8908,13 @@
         <v>180445636.191136</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>207561076.5051768</v>
+        <v>207561076.5051767</v>
       </c>
       <c r="P85" s="183" t="n">
         <v>239167997.8382463</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>279363794.6181195</v>
+        <v>279363794.6181194</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>1250.735051795708</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>1317.254015613915</v>
+        <v>1317.254015613914</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>156399614.669129</v>
@@ -8958,13 +8958,13 @@
         <v>180445636.191136</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>207561076.5051768</v>
+        <v>207561076.5051767</v>
       </c>
       <c r="AG85" s="189" t="n">
         <v>239167997.8382463</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>279363794.6181195</v>
+        <v>279363794.6181194</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9768,7 +9768,7 @@
         <v>176267.6236656359</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>195239.0332577241</v>
+        <v>195239.0332577242</v>
       </c>
       <c r="H94" s="85" t="n">
         <v>1270.098661326248</v>
@@ -9824,7 +9824,7 @@
         <v>1071.011065912703</v>
       </c>
       <c r="Z94" s="86" t="n">
-        <v>859.4261510053072</v>
+        <v>859.4261510053074</v>
       </c>
       <c r="AA94" s="86" t="n">
         <v>632.2156204549408</v>
@@ -10012,7 +10012,7 @@
         <v>749.020863243838</v>
       </c>
       <c r="K96" s="133" t="n">
-        <v>451.4780180637046</v>
+        <v>451.4780180637045</v>
       </c>
       <c r="L96" s="134" t="n">
         <v>108.8020879108765</v>
@@ -10030,7 +10030,7 @@
         <v>189877.7044281543</v>
       </c>
       <c r="Q96" s="134" t="n">
-        <v>210319.0415807613</v>
+        <v>210319.0415807614</v>
       </c>
       <c r="S96" s="51" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>175627.4975613213</v>
       </c>
       <c r="W96" s="136" t="n">
-        <v>190838.4992905266</v>
+        <v>190838.4992905267</v>
       </c>
       <c r="X96" s="137" t="n">
         <v>211984.1925639558</v>
@@ -10056,7 +10056,7 @@
         <v>1072.081569346541</v>
       </c>
       <c r="Z96" s="136" t="n">
-        <v>860.5244661116376</v>
+        <v>860.5244661116377</v>
       </c>
       <c r="AA96" s="136" t="n">
         <v>633.3473133561454</v>
@@ -10065,7 +10065,7 @@
         <v>383.4525488077977</v>
       </c>
       <c r="AC96" s="137" t="n">
-        <v>96.23483023983755</v>
+        <v>96.23483023983754</v>
       </c>
       <c r="AD96" s="135" t="n">
         <v>153981.4117751766</v>
@@ -10077,10 +10077,10 @@
         <v>176260.8448746775</v>
       </c>
       <c r="AG96" s="136" t="n">
-        <v>191221.9518393344</v>
+        <v>191221.9518393345</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>212080.4273941956</v>
+        <v>212080.4273941957</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
